--- a/data/trans_bre/IP19C02-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C02-Estudios-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 20,97</t>
+          <t>2,12; 19,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 6,82</t>
+          <t>-7,29; 6,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-31,22; 11,01</t>
+          <t>-30,87; 11,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-32,82; 21,89</t>
+          <t>-31,93; 22,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,46; —</t>
+          <t>-12,27; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-67,97; 43,62</t>
+          <t>-67,28; 40,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-56,08; 72,97</t>
+          <t>-55,91; 75,05</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 3,51</t>
+          <t>-3,36; 3,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 3,78</t>
+          <t>-3,67; 3,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 4,47</t>
+          <t>-6,69; 4,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 3,57</t>
+          <t>-10,8; 4,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,06; 73,46</t>
+          <t>-41,08; 80,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,07; 92,69</t>
+          <t>-48,84; 90,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,89; 26,38</t>
+          <t>-28,98; 29,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,94; 11,82</t>
+          <t>-28,62; 14,16</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 3,59</t>
+          <t>-11,07; 3,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 3,06</t>
+          <t>-10,17; 3,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 15,14</t>
+          <t>-3,07; 15,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 9,3</t>
+          <t>-9,74; 10,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-81,8; 81,55</t>
+          <t>-79,14; 92,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-80,87; 75,92</t>
+          <t>-78,17; 67,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-22,34; 191,96</t>
+          <t>-20,67; 189,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-34,02; 46,72</t>
+          <t>-32,84; 49,38</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 4,07</t>
+          <t>-2,55; 3,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 2,05</t>
+          <t>-3,59; 2,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 4,28</t>
+          <t>-5,43; 4,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 3,65</t>
+          <t>-7,81; 3,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,06; 77,58</t>
+          <t>-30,53; 69,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,59; 44,06</t>
+          <t>-46,43; 50,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 24,11</t>
+          <t>-25,77; 23,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 13,52</t>
+          <t>-22,44; 13,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C02-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C02-Estudios-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 19,95</t>
+          <t>2,12; 20,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 6,49</t>
+          <t>-6,52; 6,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,87; 11,32</t>
+          <t>-35,76; 8,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-31,93; 22,79</t>
+          <t>-32,6; 21,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,27; —</t>
+          <t>-13,52; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-67,28; 40,55</t>
+          <t>-72,14; 38,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-55,91; 75,05</t>
+          <t>-57,48; 67,56</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 3,84</t>
+          <t>-3,64; 3,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 3,84</t>
+          <t>-3,46; 3,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 4,97</t>
+          <t>-7,6; 3,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 4,06</t>
+          <t>-10,63; 3,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,08; 80,89</t>
+          <t>-44,22; 83,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,84; 90,0</t>
+          <t>-42,9; 88,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,98; 29,5</t>
+          <t>-32,28; 23,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,62; 14,16</t>
+          <t>-28,77; 12,84</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 3,64</t>
+          <t>-11,44; 3,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 3,26</t>
+          <t>-10,01; 3,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 15,16</t>
+          <t>-3,14; 14,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 10,17</t>
+          <t>-8,5; 9,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-79,14; 92,68</t>
+          <t>-82,38; 70,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-78,17; 67,69</t>
+          <t>-77,02; 94,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 189,17</t>
+          <t>-23,74; 189,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-32,84; 49,38</t>
+          <t>-30,05; 46,38</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 3,63</t>
+          <t>-2,48; 3,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 2,42</t>
+          <t>-3,58; 2,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 4,1</t>
+          <t>-5,4; 4,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 3,82</t>
+          <t>-7,65; 4,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,53; 69,16</t>
+          <t>-31,15; 75,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,43; 50,32</t>
+          <t>-45,53; 46,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 23,68</t>
+          <t>-24,55; 26,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 13,13</t>
+          <t>-22,3; 15,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C02-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C02-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-6,32</t>
+          <t>-7,35</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-13,8%</t>
+          <t>-14,95%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 20,01</t>
+          <t>2,06; 20,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 6,66</t>
+          <t>-5,92; 6,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-35,76; 8,35</t>
+          <t>-31,22; 11,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-32,6; 21,29</t>
+          <t>-31,84; 19,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,52; —</t>
+          <t>-12,46; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-72,14; 38,55</t>
+          <t>-67,97; 43,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-57,48; 67,56</t>
+          <t>-52,83; 59,54</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,91</t>
+          <t>-2,73</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-8,77%</t>
+          <t>-7,77%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 3,6</t>
+          <t>-3,52; 3,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 3,69</t>
+          <t>-3,39; 3,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 3,87</t>
+          <t>-7,75; 4,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 3,81</t>
+          <t>-10,62; 4,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,22; 83,55</t>
+          <t>-43,06; 73,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,9; 88,49</t>
+          <t>-45,07; 92,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,28; 23,22</t>
+          <t>-32,89; 26,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,77; 12,84</t>
+          <t>-26,58; 12,46</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>-4,87%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 3,03</t>
+          <t>-10,81; 3,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 3,74</t>
+          <t>-10,12; 3,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 14,79</t>
+          <t>-2,9; 15,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 9,77</t>
+          <t>-12,2; 7,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-82,38; 70,76</t>
+          <t>-81,8; 81,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-77,02; 94,5</t>
+          <t>-80,87; 75,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,74; 189,37</t>
+          <t>-22,34; 191,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-30,05; 46,38</t>
+          <t>-37,74; 35,3</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,78</t>
+          <t>-2,36</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-5,64%</t>
+          <t>-6,99%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 3,83</t>
+          <t>-2,18; 4,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 2,19</t>
+          <t>-3,45; 2,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 4,63</t>
+          <t>-5,33; 4,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 4,39</t>
+          <t>-8,31; 2,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,15; 75,54</t>
+          <t>-28,06; 77,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,53; 46,43</t>
+          <t>-43,59; 44,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,55; 26,7</t>
+          <t>-24,63; 24,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,3; 15,02</t>
+          <t>-22,64; 10,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C02-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C02-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,193 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>10,81</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,64</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-11,28</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-7,35</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>342,36%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,54%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-29,89%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-14,95%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>10.80762998920043</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.6360212784977254</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-11.27711768017006</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-7.354233920327835</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>3.423641065181352</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.185365951746003</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.2988837540895504</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.1495187153545157</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2,06; 20,97</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,92; 6,82</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-31,22; 11,01</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-31,84; 19,47</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-12,46; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-67,97; 43,62</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-52,83; 59,54</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2.056661606998254</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.915180389529903</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-31.22401876852374</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-31.84450684900038</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.1245953577406918</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="n">
+        <v>-0.679697960945432</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.5283370227940166</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>20.96536185755521</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.823024135758564</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>11.01085399516451</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>19.46943484399121</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="n">
+        <v>0.436210317182845</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.5953653995926271</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,31</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,73</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-0,32%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-6,5%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-7,77%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,52; 3,51</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,39; 3,78</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-7,75; 4,47</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-10,62; 4,09</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-43,06; 73,46</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-45,07; 92,69</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-32,89; 26,38</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-26,58; 12,46</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.02063024596578034</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.06745195695124842</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.308106388490465</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-2.729557001284211</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.00316686470767066</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.0112119455657321</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.06501535325288493</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.07770038059560203</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,51</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,93</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,46</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,33</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-37,86%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-33,17%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>45,21%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-4,87%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.520038774375074</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.394819083565887</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-7.749137606743943</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-10.62099462860419</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4306293665998625</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4507389417397872</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.3288546611440988</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.2658293293174581</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-10,81; 3,59</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-10,12; 3,06</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-2,9; 15,14</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-12,2; 7,9</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-81,8; 81,55</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-80,87; 75,92</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-22,34; 191,96</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-37,74; 35,3</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.509993295019543</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.775343641269489</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.472088343969213</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.085116715361752</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.7346250926735084</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.9268873213531607</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.2637980751487245</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.1245536299870598</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +813,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,36</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-9,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-2,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-6,99%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-3.510231956384922</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.925250415761529</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>5.456255993155406</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.331453858223619</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.3785528824087641</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.3316560224459714</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.4520900250143835</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.04874811487506069</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,18; 4,07</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,45; 2,05</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-5,33; 4,28</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-8,31; 2,95</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-28,06; 77,58</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-43,59; 44,06</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-24,63; 24,11</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-22,64; 10,19</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-10.80894312677894</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-10.11799119361799</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.902097020030006</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-12.1950107698965</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.8179878495663107</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.8087055337674024</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.2234280440299835</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.377358227929229</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.590616358668815</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.061652199048875</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>15.13575244103047</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>7.904874988139181</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.8155038077793946</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.7591535101996434</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.919576570173582</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.3530183465173941</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.6611939300429026</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.5777745524376786</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.5809774516852995</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2.356307878525499</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.09907249671699263</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.09110525685313917</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.02972046326396993</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.06989419700704971</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.17772021726706</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.453172613381513</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-5.331072946638328</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-8.306906683862545</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2805663234190969</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.435860963293157</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.2462828515585462</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.226380468656766</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>4.068503744071744</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.051364992515159</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.276837228951448</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.94573267037387</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.7757620599852281</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.44057784555687</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.2410626470452018</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.1019280319824159</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1011,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
